--- a/tables/datas/__enums__.xlsx
+++ b/tables/datas/__enums__.xlsx
@@ -1,304 +1,177 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="15615" windowHeight="7560"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="15615" windowHeight="7560" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <definedNames/>
+  <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>full_name</t>
-  </si>
-  <si>
-    <t>flags</t>
-  </si>
-  <si>
-    <t>unique</t>
-  </si>
-  <si>
-    <t>group</t>
-  </si>
-  <si>
-    <t>comment</t>
-  </si>
-  <si>
-    <t>tags</t>
-  </si>
-  <si>
-    <t>*items</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>alias</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>全名(包含模块和名字)</t>
-  </si>
-  <si>
-    <t>是否为标志类（即每个枚举项为位标记，例如System.IO.FileMode,填数据时可以为READ|WRITE这样)</t>
-  </si>
-  <si>
-    <t>枚举项是否唯一</t>
-  </si>
-  <si>
-    <t>枚举名</t>
-  </si>
-  <si>
-    <t>别名</t>
-  </si>
-  <si>
-    <t>值</t>
-  </si>
-  <si>
-    <t>注释</t>
-  </si>
-  <si>
-    <t>test.ETestQuality</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>白</t>
-  </si>
-  <si>
-    <t>最高品质</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>黑</t>
-  </si>
-  <si>
-    <t>黑色的</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>蓝</t>
-  </si>
-  <si>
-    <t>蓝色的</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>红</t>
-  </si>
-  <si>
-    <t>最差品质</t>
-  </si>
-  <si>
-    <t>test.AccessFlag</t>
-  </si>
-  <si>
-    <t>WRITE</t>
-  </si>
-  <si>
-    <t>READ</t>
-  </si>
-  <si>
-    <t>TRUNCATE</t>
-  </si>
-  <si>
-    <t>NEW</t>
-  </si>
-  <si>
-    <t>READ_WRITE</t>
-  </si>
-  <si>
-    <t>WRITE|READ</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="20">
     <font>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <b val="1"/>
+      <color theme="3"/>
       <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <b val="1"/>
       <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -598,161 +471,162 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -806,11 +680,74 @@
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1070,216 +1007,362 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:L12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="8.24761904761905" customWidth="1"/>
-    <col min="4" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="9.38095238095238" customWidth="1"/>
-    <col min="7" max="7" width="7.57142857142857" customWidth="1"/>
-    <col min="8" max="8" width="13.5047619047619" customWidth="1"/>
-    <col min="10" max="10" width="12.6285714285714" customWidth="1"/>
+    <col width="19" customWidth="1" style="2" min="2" max="2"/>
+    <col width="8.24761904761905" customWidth="1" style="2" min="3" max="3"/>
+    <col width="10" customWidth="1" style="2" min="4" max="5"/>
+    <col width="9.38095238095238" customWidth="1" style="2" min="6" max="6"/>
+    <col width="7.57142857142857" customWidth="1" style="2" min="7" max="7"/>
+    <col width="13.5047619047619" customWidth="1" style="2" min="8" max="8"/>
+    <col width="12.6285714285714" customWidth="1" style="2" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>full_name</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>flags</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>*items</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="H2" s="0" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="I2" s="0" t="inlineStr">
+        <is>
+          <t>alias</t>
+        </is>
+      </c>
+      <c r="J2" s="0" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="K2" s="0" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="L2" s="0" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>全名(包含模块和名字)</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>是否为标志类（即每个枚举项为位标记，例如System.IO.FileMode,填数据时可以为READ|WRITE这样)</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>枚举项是否唯一</t>
+        </is>
+      </c>
+      <c r="H3" s="0" t="inlineStr">
+        <is>
+          <t>枚举名</t>
+        </is>
+      </c>
+      <c r="I3" s="0" t="inlineStr">
+        <is>
+          <t>别名</t>
+        </is>
+      </c>
+      <c r="J3" s="0" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="K3" s="0" t="inlineStr">
+        <is>
+          <t>注释</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>test.ETestQuality</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D4" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="H4" s="0" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I4" s="0" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="J4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="0" t="inlineStr">
+        <is>
+          <t>最高品质</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="H5" s="0" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I5" s="0" t="inlineStr">
+        <is>
+          <t>黑</t>
+        </is>
+      </c>
+      <c r="J5" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="K5" s="0" t="inlineStr">
+        <is>
+          <t>黑色的</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="H6" s="0" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I6" s="0" t="inlineStr">
+        <is>
+          <t>蓝</t>
+        </is>
+      </c>
+      <c r="J6" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="K6" s="0" t="inlineStr">
+        <is>
+          <t>蓝色的</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="H7" s="0" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I7" s="0" t="inlineStr">
+        <is>
+          <t>红</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" t="s">
+      <c r="K7" s="0" t="inlineStr">
+        <is>
+          <t>最差品质</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>test.AccessFlag</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="D8" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" s="0" t="inlineStr">
+        <is>
+          <t>WRITE</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="H9" s="0" t="inlineStr">
+        <is>
+          <t>READ</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="H10" s="0" t="inlineStr">
+        <is>
+          <t>TRUNCATE</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="H11" s="0" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="H12" s="0" t="inlineStr">
+        <is>
+          <t>READ_WRITE</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="inlineStr">
+        <is>
+          <t>WRITE|READ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>common.EMonsterAttr</t>
+        </is>
+      </c>
+      <c r="C13" t="b">
         <v>0</v>
       </c>
-      <c r="H2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" t="s">
-        <v>5</v>
-      </c>
-      <c r="L2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="2:11">
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D4" t="b">
+      <c r="D13" t="b">
         <v>1</v>
       </c>
-      <c r="H4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J4">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>怪物属性类型</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>生命值</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="8:11">
-      <c r="H5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5">
+      <c r="K13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>ATK</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>攻击力</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
         <v>2</v>
       </c>
-      <c r="K5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="8:11">
-      <c r="H6" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6">
+      <c r="K14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>防御力</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
         <v>3</v>
       </c>
-      <c r="K6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="8:11">
-      <c r="H7" t="s">
-        <v>29</v>
-      </c>
-      <c r="I7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J7">
-        <v>4</v>
-      </c>
-      <c r="K7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10">
-      <c r="B8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" t="b">
-        <v>1</v>
-      </c>
-      <c r="D8" t="b">
-        <v>1</v>
-      </c>
-      <c r="H8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="8:10">
-      <c r="H9" t="s">
-        <v>34</v>
-      </c>
-      <c r="J9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="8:10">
-      <c r="H10" t="s">
-        <v>35</v>
-      </c>
-      <c r="J10">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="8:10">
-      <c r="H11" t="s">
-        <v>36</v>
-      </c>
-      <c r="J11">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="8:10">
-      <c r="H12" t="s">
-        <v>37</v>
-      </c>
-      <c r="J12" t="s">
-        <v>38</v>
-      </c>
+      <c r="K15" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/tables/datas/__enums__.xlsx
+++ b/tables/datas/__enums__.xlsx
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" style="2" min="2" max="2"/>
@@ -1295,68 +1295,402 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t>common.EMonsterAttr</t>
         </is>
       </c>
-      <c r="C13" t="b">
+      <c r="C13" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D13" t="b">
+      <c r="D13" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="0" t="inlineStr">
         <is>
           <t>怪物属性类型</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="0" t="inlineStr">
         <is>
           <t>HP</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" s="0" t="inlineStr">
         <is>
           <t>生命值</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="J13" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" s="0" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="0" t="inlineStr">
         <is>
           <t>ATK</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" s="0" t="inlineStr">
         <is>
           <t>攻击力</t>
         </is>
       </c>
-      <c r="J14" t="n">
+      <c r="J14" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" s="0" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="0" t="inlineStr">
         <is>
           <t>DEF</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" s="0" t="inlineStr">
         <is>
           <t>防御力</t>
         </is>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" s="0" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="H16" s="0" t="inlineStr">
+        <is>
+          <t>AGILITY</t>
+        </is>
+      </c>
+      <c r="I16" s="0" t="inlineStr">
+        <is>
+          <t>敏捷</t>
+        </is>
+      </c>
+      <c r="J16" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t>common.ESkillTargetType</t>
+        </is>
+      </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>common.ESkillTargetType</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="D17" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" s="0" t="inlineStr">
+        <is>
+          <t>技能目标类型</t>
+        </is>
+      </c>
+      <c r="H17" s="0" t="inlineStr">
+        <is>
+          <t>SingleEnemy</t>
+        </is>
+      </c>
+      <c r="I17" s="0" t="inlineStr">
+        <is>
+          <t>单体敌方</t>
+        </is>
+      </c>
+      <c r="J17" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" s="0" t="inlineStr">
+        <is>
+          <t>单体敌方</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="H18" s="0" t="inlineStr">
+        <is>
+          <t>AllEnemiesInRange</t>
+        </is>
+      </c>
+      <c r="I18" s="0" t="inlineStr">
+        <is>
+          <t>范围敌方</t>
+        </is>
+      </c>
+      <c r="J18" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" s="0" t="inlineStr">
+        <is>
+          <t>范围敌方</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="H19" s="0" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="I19" s="0" t="inlineStr">
+        <is>
+          <t>自身</t>
+        </is>
+      </c>
+      <c r="J19" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="K19" s="0" t="inlineStr">
+        <is>
+          <t>自身</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="inlineStr">
+        <is>
+          <t>common.ECombatActionType</t>
+        </is>
+      </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>common.ECombatActionType</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="D20" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="F20" s="0" t="inlineStr">
+        <is>
+          <t>战斗动作类型</t>
+        </is>
+      </c>
+      <c r="H20" s="0" t="inlineStr">
+        <is>
+          <t>DealDamage</t>
+        </is>
+      </c>
+      <c r="I20" s="0" t="inlineStr">
+        <is>
+          <t>造成伤害</t>
+        </is>
+      </c>
+      <c r="J20" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" s="0" t="inlineStr">
+        <is>
+          <t>造成伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="H21" s="0" t="inlineStr">
+        <is>
+          <t>InterruptCast</t>
+        </is>
+      </c>
+      <c r="I21" s="0" t="inlineStr">
+        <is>
+          <t>打断施法</t>
+        </is>
+      </c>
+      <c r="J21" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" s="0" t="inlineStr">
+        <is>
+          <t>打断施法</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="inlineStr">
+        <is>
+          <t>common.EDamageType</t>
+        </is>
+      </c>
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t>common.EDamageType</t>
+        </is>
+      </c>
+      <c r="C22" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="D22" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="F22" s="0" t="inlineStr">
+        <is>
+          <t>伤害类型</t>
+        </is>
+      </c>
+      <c r="H22" s="0" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="I22" s="0" t="inlineStr">
+        <is>
+          <t>物理</t>
+        </is>
+      </c>
+      <c r="J22" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" s="0" t="inlineStr">
+        <is>
+          <t>物理</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="H23" s="0" t="inlineStr">
+        <is>
+          <t>Magical</t>
+        </is>
+      </c>
+      <c r="I23" s="0" t="inlineStr">
+        <is>
+          <t>魔法</t>
+        </is>
+      </c>
+      <c r="J23" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" s="0" t="inlineStr">
+        <is>
+          <t>魔法</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="0" t="inlineStr">
+        <is>
+          <t>common.EJobType</t>
+        </is>
+      </c>
+      <c r="C24" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="D24" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="G24" s="0" t="inlineStr">
+        <is>
+          <t>职业类型</t>
+        </is>
+      </c>
+      <c r="H24" s="0" t="inlineStr">
+        <is>
+          <t>Warrior</t>
+        </is>
+      </c>
+      <c r="I24" s="0" t="inlineStr">
+        <is>
+          <t>战士</t>
+        </is>
+      </c>
+      <c r="J24" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" s="0" t="inlineStr">
+        <is>
+          <t>战士</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="H25" s="0" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="I25" s="0" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="J25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="0" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="H26" s="0" t="inlineStr">
+        <is>
+          <t>Mage</t>
+        </is>
+      </c>
+      <c r="I26" s="0" t="inlineStr">
+        <is>
+          <t>法师</t>
+        </is>
+      </c>
+      <c r="J26" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K26" s="0" t="inlineStr">
+        <is>
+          <t>法师</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="H27" s="0" t="inlineStr">
+        <is>
+          <t>Priest</t>
+        </is>
+      </c>
+      <c r="I27" s="0" t="inlineStr">
+        <is>
+          <t>牧师</t>
+        </is>
+      </c>
+      <c r="J27" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="K27" s="0" t="inlineStr">
+        <is>
+          <t>牧师</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="H28" s="0" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="I28" s="0" t="inlineStr">
+        <is>
+          <t>怪物</t>
+        </is>
+      </c>
+      <c r="J28" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="K28" s="0" t="inlineStr">
+        <is>
+          <t>怪物</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/tables/datas/__enums__.xlsx
+++ b/tables/datas/__enums__.xlsx
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" style="2" min="2" max="2"/>
@@ -1516,131 +1516,115 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="0" t="inlineStr">
-        <is>
-          <t>common.EDamageType</t>
-        </is>
-      </c>
-      <c r="B22" s="0" t="inlineStr">
-        <is>
-          <t>common.EDamageType</t>
-        </is>
-      </c>
-      <c r="C22" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="D22" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="F22" s="0" t="inlineStr">
-        <is>
-          <t>伤害类型</t>
-        </is>
-      </c>
       <c r="H22" s="0" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>ApplyBuff</t>
         </is>
       </c>
       <c r="I22" s="0" t="inlineStr">
         <is>
-          <t>物理</t>
+          <t>施加Buff</t>
         </is>
       </c>
       <c r="J22" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K22" s="0" t="inlineStr">
         <is>
-          <t>物理</t>
+          <t>施加Buff</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="H23" s="0" t="inlineStr">
         <is>
-          <t>Magical</t>
+          <t>ApplyShield</t>
         </is>
       </c>
       <c r="I23" s="0" t="inlineStr">
         <is>
-          <t>魔法</t>
+          <t>施加护盾</t>
         </is>
       </c>
       <c r="J23" s="0" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K23" s="0" t="inlineStr">
         <is>
-          <t>魔法</t>
+          <t>施加护盾</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="0" t="inlineStr">
-        <is>
-          <t>common.EJobType</t>
-        </is>
-      </c>
-      <c r="C24" s="0" t="b">
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Purify</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>净化</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>6</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>移除Debuff</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="inlineStr">
+        <is>
+          <t>common.EDamageType</t>
+        </is>
+      </c>
+      <c r="B25" s="0" t="inlineStr">
+        <is>
+          <t>common.EDamageType</t>
+        </is>
+      </c>
+      <c r="C25" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D24" s="0" t="b">
+      <c r="D25" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="G24" s="0" t="inlineStr">
-        <is>
-          <t>职业类型</t>
-        </is>
-      </c>
-      <c r="H24" s="0" t="inlineStr">
-        <is>
-          <t>Warrior</t>
-        </is>
-      </c>
-      <c r="I24" s="0" t="inlineStr">
-        <is>
-          <t>战士</t>
-        </is>
-      </c>
-      <c r="J24" s="0" t="n">
+      <c r="F25" s="0" t="inlineStr">
+        <is>
+          <t>伤害类型</t>
+        </is>
+      </c>
+      <c r="H25" s="0" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="I25" s="0" t="inlineStr">
+        <is>
+          <t>物理</t>
+        </is>
+      </c>
+      <c r="J25" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="K24" s="0" t="inlineStr">
-        <is>
-          <t>战士</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="H25" s="0" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="I25" s="0" t="inlineStr">
-        <is>
-          <t>通用</t>
-        </is>
-      </c>
-      <c r="J25" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="K25" s="0" t="inlineStr">
         <is>
-          <t>通用</t>
+          <t>物理</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="H26" s="0" t="inlineStr">
         <is>
-          <t>Mage</t>
+          <t>Magical</t>
         </is>
       </c>
       <c r="I26" s="0" t="inlineStr">
         <is>
-          <t>法师</t>
+          <t>魔法</t>
         </is>
       </c>
       <c r="J26" s="0" t="n">
@@ -1648,47 +1632,381 @@
       </c>
       <c r="K26" s="0" t="inlineStr">
         <is>
-          <t>法师</t>
+          <t>魔法</t>
         </is>
       </c>
     </row>
     <row r="27">
+      <c r="B27" s="0" t="inlineStr">
+        <is>
+          <t>common.EJobType</t>
+        </is>
+      </c>
+      <c r="C27" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="D27" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="G27" s="0" t="inlineStr">
+        <is>
+          <t>职业类型</t>
+        </is>
+      </c>
       <c r="H27" s="0" t="inlineStr">
         <is>
-          <t>Priest</t>
+          <t>Warrior</t>
         </is>
       </c>
       <c r="I27" s="0" t="inlineStr">
         <is>
-          <t>牧师</t>
+          <t>战士</t>
         </is>
       </c>
       <c r="J27" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K27" s="0" t="inlineStr">
         <is>
-          <t>牧师</t>
+          <t>战士</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="H28" s="0" t="inlineStr">
         <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="I28" s="0" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="J28" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="0" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="H29" s="0" t="inlineStr">
+        <is>
+          <t>Mage</t>
+        </is>
+      </c>
+      <c r="I29" s="0" t="inlineStr">
+        <is>
+          <t>法师</t>
+        </is>
+      </c>
+      <c r="J29" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K29" s="0" t="inlineStr">
+        <is>
+          <t>法师</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="H30" s="0" t="inlineStr">
+        <is>
+          <t>Priest</t>
+        </is>
+      </c>
+      <c r="I30" s="0" t="inlineStr">
+        <is>
+          <t>牧师</t>
+        </is>
+      </c>
+      <c r="J30" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="K30" s="0" t="inlineStr">
+        <is>
+          <t>牧师</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="H31" s="0" t="inlineStr">
+        <is>
           <t>Monster</t>
         </is>
       </c>
-      <c r="I28" s="0" t="inlineStr">
+      <c r="I31" s="0" t="inlineStr">
         <is>
           <t>怪物</t>
         </is>
       </c>
-      <c r="J28" s="0" t="n">
+      <c r="J31" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="K28" s="0" t="inlineStr">
+      <c r="K31" s="0" t="inlineStr">
         <is>
           <t>怪物</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="inlineStr">
+        <is>
+          <t>common.ECombatLogType</t>
+        </is>
+      </c>
+      <c r="B32" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="C32" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" s="0" t="inlineStr">
+        <is>
+          <t>战斗日志文本类型</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="H33" s="0" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="I33" s="0" t="inlineStr">
+        <is>
+          <t>战斗开始</t>
+        </is>
+      </c>
+      <c r="J33" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="0" t="inlineStr">
+        <is>
+          <t>可用参数: {actor} {target}</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="H34" s="0" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="I34" s="0" t="inlineStr">
+        <is>
+          <t>释放技能</t>
+        </is>
+      </c>
+      <c r="J34" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" s="0" t="inlineStr">
+        <is>
+          <t>可用参数: {actor} {skill}</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="H35" s="0" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="I35" s="0" t="inlineStr">
+        <is>
+          <t>造成伤害</t>
+        </is>
+      </c>
+      <c r="J35" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K35" s="0" t="inlineStr">
+        <is>
+          <t>可用参数: {actor} {target} {value}</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="H36" s="0" t="inlineStr">
+        <is>
+          <t>Heal</t>
+        </is>
+      </c>
+      <c r="I36" s="0" t="inlineStr">
+        <is>
+          <t>治疗回血</t>
+        </is>
+      </c>
+      <c r="J36" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="K36" s="0" t="inlineStr">
+        <is>
+          <t>可用参数: {actor} {value}</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="H37" s="0" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="I37" s="0" t="inlineStr">
+        <is>
+          <t>获得Buff</t>
+        </is>
+      </c>
+      <c r="J37" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="K37" s="0" t="inlineStr">
+        <is>
+          <t>可用参数: {actor} {extra}</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="H38" s="0" t="inlineStr">
+        <is>
+          <t>Dodge</t>
+        </is>
+      </c>
+      <c r="I38" s="0" t="inlineStr">
+        <is>
+          <t>打空</t>
+        </is>
+      </c>
+      <c r="J38" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="K38" s="0" t="inlineStr">
+        <is>
+          <t>可用参数: {actor} {skill}</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="H39" s="0" t="inlineStr">
+        <is>
+          <t>Death</t>
+        </is>
+      </c>
+      <c r="I39" s="0" t="inlineStr">
+        <is>
+          <t>死亡</t>
+        </is>
+      </c>
+      <c r="J39" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="K39" s="0" t="inlineStr">
+        <is>
+          <t>可用参数: {actor} {extra}</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="H40" s="0" t="inlineStr">
+        <is>
+          <t>End</t>
+        </is>
+      </c>
+      <c r="I40" s="0" t="inlineStr">
+        <is>
+          <t>战斗结束</t>
+        </is>
+      </c>
+      <c r="J40" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="K40" s="0" t="inlineStr">
+        <is>
+          <t>可用参数: {actor} {extra}</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="H41" s="0" t="inlineStr">
+        <is>
+          <t>BuffApply</t>
+        </is>
+      </c>
+      <c r="I41" s="0" t="inlineStr">
+        <is>
+          <t>施加Buff</t>
+        </is>
+      </c>
+      <c r="J41" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="K41" s="0" t="inlineStr">
+        <is>
+          <t>可用参数: {actor} {target} {extra}</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="H42" s="0" t="inlineStr">
+        <is>
+          <t>BuffRemove</t>
+        </is>
+      </c>
+      <c r="I42" s="0" t="inlineStr">
+        <is>
+          <t>Buff消失</t>
+        </is>
+      </c>
+      <c r="J42" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="K42" s="0" t="inlineStr">
+        <is>
+          <t>可用参数: {target} {extra}</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="H43" s="0" t="inlineStr">
+        <is>
+          <t>BuffTick</t>
+        </is>
+      </c>
+      <c r="I43" s="0" t="inlineStr">
+        <is>
+          <t>Buff持续伤害</t>
+        </is>
+      </c>
+      <c r="J43" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="K43" s="0" t="inlineStr">
+        <is>
+          <t>可用参数: {target} {extra} {value}</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="H44" s="0" t="inlineStr">
+        <is>
+          <t>ShieldAbsorb</t>
+        </is>
+      </c>
+      <c r="I44" s="0" t="inlineStr">
+        <is>
+          <t>护盾吸收</t>
+        </is>
+      </c>
+      <c r="J44" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="K44" s="0" t="inlineStr">
+        <is>
+          <t>可用参数: {target} {value}</t>
         </is>
       </c>
     </row>

--- a/tables/datas/__enums__.xlsx
+++ b/tables/datas/__enums__.xlsx
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L54"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" style="2" min="2" max="2"/>
@@ -1455,474 +1455,474 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="0" t="inlineStr">
+      <c r="H20" s="0" t="inlineStr">
+        <is>
+          <t>AllAlliesInRange</t>
+        </is>
+      </c>
+      <c r="I20" s="0" t="inlineStr">
+        <is>
+          <t>范围内友方</t>
+        </is>
+      </c>
+      <c r="J20" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="K20" s="0" t="inlineStr">
+        <is>
+          <t>范围内友方</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="inlineStr">
         <is>
           <t>common.ECombatActionType</t>
         </is>
       </c>
-      <c r="B20" s="0" t="inlineStr">
+      <c r="B21" s="0" t="inlineStr">
         <is>
           <t>common.ECombatActionType</t>
         </is>
       </c>
-      <c r="C20" s="0" t="b">
+      <c r="C21" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D20" s="0" t="b">
+      <c r="D21" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="F20" s="0" t="inlineStr">
+      <c r="F21" s="0" t="inlineStr">
         <is>
           <t>战斗动作类型</t>
         </is>
       </c>
-      <c r="H20" s="0" t="inlineStr">
+      <c r="H21" s="0" t="inlineStr">
         <is>
           <t>DealDamage</t>
         </is>
       </c>
-      <c r="I20" s="0" t="inlineStr">
+      <c r="I21" s="0" t="inlineStr">
         <is>
           <t>造成伤害</t>
         </is>
       </c>
-      <c r="J20" s="0" t="n">
+      <c r="J21" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="K20" s="0" t="inlineStr">
+      <c r="K21" s="0" t="inlineStr">
         <is>
           <t>造成伤害</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="H21" s="0" t="inlineStr">
-        <is>
-          <t>InterruptCast</t>
-        </is>
-      </c>
-      <c r="I21" s="0" t="inlineStr">
-        <is>
-          <t>打断施法</t>
-        </is>
-      </c>
-      <c r="J21" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="K21" s="0" t="inlineStr">
-        <is>
-          <t>打断施法</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="H22" s="0" t="inlineStr">
         <is>
-          <t>ApplyBuff</t>
+          <t>InterruptCast</t>
         </is>
       </c>
       <c r="I22" s="0" t="inlineStr">
         <is>
-          <t>施加Buff</t>
+          <t>打断施法</t>
         </is>
       </c>
       <c r="J22" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K22" s="0" t="inlineStr">
         <is>
-          <t>施加Buff</t>
+          <t>打断施法</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="H23" s="0" t="inlineStr">
         <is>
+          <t>ApplyBuff</t>
+        </is>
+      </c>
+      <c r="I23" s="0" t="inlineStr">
+        <is>
+          <t>施加Buff</t>
+        </is>
+      </c>
+      <c r="J23" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="K23" s="0" t="inlineStr">
+        <is>
+          <t>施加Buff</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="H24" s="0" t="inlineStr">
+        <is>
           <t>ApplyShield</t>
         </is>
       </c>
-      <c r="I23" s="0" t="inlineStr">
+      <c r="I24" s="0" t="inlineStr">
         <is>
           <t>施加护盾</t>
         </is>
       </c>
-      <c r="J23" s="0" t="n">
+      <c r="J24" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="K23" s="0" t="inlineStr">
+      <c r="K24" s="0" t="inlineStr">
         <is>
           <t>施加护盾</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="H24" t="inlineStr">
+    <row r="25">
+      <c r="H25" s="0" t="inlineStr">
         <is>
           <t>Purify</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I25" s="0" t="inlineStr">
         <is>
           <t>净化</t>
         </is>
       </c>
-      <c r="J24" t="n">
+      <c r="J25" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K25" s="0" t="inlineStr">
         <is>
           <t>移除Debuff</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="0" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="0" t="inlineStr">
         <is>
           <t>common.EDamageType</t>
         </is>
       </c>
-      <c r="B25" s="0" t="inlineStr">
+      <c r="B26" s="0" t="inlineStr">
         <is>
           <t>common.EDamageType</t>
         </is>
       </c>
-      <c r="C25" s="0" t="b">
+      <c r="C26" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D25" s="0" t="b">
+      <c r="D26" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="F25" s="0" t="inlineStr">
+      <c r="F26" s="0" t="inlineStr">
         <is>
           <t>伤害类型</t>
         </is>
       </c>
-      <c r="H25" s="0" t="inlineStr">
+      <c r="H26" s="0" t="inlineStr">
         <is>
           <t>Physical</t>
         </is>
       </c>
-      <c r="I25" s="0" t="inlineStr">
+      <c r="I26" s="0" t="inlineStr">
         <is>
           <t>物理</t>
         </is>
       </c>
-      <c r="J25" s="0" t="n">
+      <c r="J26" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="K25" s="0" t="inlineStr">
+      <c r="K26" s="0" t="inlineStr">
         <is>
           <t>物理</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="H26" s="0" t="inlineStr">
+    <row r="27">
+      <c r="H27" s="0" t="inlineStr">
         <is>
           <t>Magical</t>
         </is>
       </c>
-      <c r="I26" s="0" t="inlineStr">
+      <c r="I27" s="0" t="inlineStr">
         <is>
           <t>魔法</t>
         </is>
       </c>
-      <c r="J26" s="0" t="n">
+      <c r="J27" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="K26" s="0" t="inlineStr">
+      <c r="K27" s="0" t="inlineStr">
         <is>
           <t>魔法</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="0" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="0" t="inlineStr">
         <is>
           <t>common.EJobType</t>
         </is>
       </c>
-      <c r="C27" s="0" t="b">
+      <c r="C28" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D27" s="0" t="b">
+      <c r="D28" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="G27" s="0" t="inlineStr">
+      <c r="G28" s="0" t="inlineStr">
         <is>
           <t>职业类型</t>
         </is>
       </c>
-      <c r="H27" s="0" t="inlineStr">
+      <c r="H28" s="0" t="inlineStr">
         <is>
           <t>Warrior</t>
         </is>
       </c>
-      <c r="I27" s="0" t="inlineStr">
+      <c r="I28" s="0" t="inlineStr">
         <is>
           <t>战士</t>
         </is>
       </c>
-      <c r="J27" s="0" t="n">
+      <c r="J28" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="K27" s="0" t="inlineStr">
+      <c r="K28" s="0" t="inlineStr">
         <is>
           <t>战士</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="H28" s="0" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="I28" s="0" t="inlineStr">
-        <is>
-          <t>通用</t>
-        </is>
-      </c>
-      <c r="J28" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" s="0" t="inlineStr">
-        <is>
-          <t>通用</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="H29" s="0" t="inlineStr">
         <is>
-          <t>Mage</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="I29" s="0" t="inlineStr">
         <is>
-          <t>法师</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="J29" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K29" s="0" t="inlineStr">
         <is>
-          <t>法师</t>
+          <t>通用</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="H30" s="0" t="inlineStr">
         <is>
-          <t>Priest</t>
+          <t>Mage</t>
         </is>
       </c>
       <c r="I30" s="0" t="inlineStr">
         <is>
-          <t>牧师</t>
+          <t>法师</t>
         </is>
       </c>
       <c r="J30" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K30" s="0" t="inlineStr">
         <is>
-          <t>牧师</t>
+          <t>法师</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="H31" s="0" t="inlineStr">
         <is>
+          <t>Priest</t>
+        </is>
+      </c>
+      <c r="I31" s="0" t="inlineStr">
+        <is>
+          <t>牧师</t>
+        </is>
+      </c>
+      <c r="J31" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="K31" s="0" t="inlineStr">
+        <is>
+          <t>牧师</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="H32" s="0" t="inlineStr">
+        <is>
           <t>Monster</t>
         </is>
       </c>
-      <c r="I31" s="0" t="inlineStr">
+      <c r="I32" s="0" t="inlineStr">
         <is>
           <t>怪物</t>
         </is>
       </c>
-      <c r="J31" s="0" t="n">
+      <c r="J32" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="K31" s="0" t="inlineStr">
+      <c r="K32" s="0" t="inlineStr">
         <is>
           <t>怪物</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="0" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="0" t="inlineStr">
         <is>
           <t>common.ECombatLogType</t>
         </is>
       </c>
-      <c r="B32" s="0" t="b">
+      <c r="B33" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="C32" s="0" t="b">
+      <c r="C33" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="G32" s="0" t="inlineStr">
+      <c r="G33" s="0" t="inlineStr">
         <is>
           <t>战斗日志文本类型</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="H33" s="0" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="I33" s="0" t="inlineStr">
-        <is>
-          <t>战斗开始</t>
-        </is>
-      </c>
-      <c r="J33" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" s="0" t="inlineStr">
-        <is>
-          <t>可用参数: {actor} {target}</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="H34" s="0" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="I34" s="0" t="inlineStr">
         <is>
-          <t>释放技能</t>
+          <t>战斗开始</t>
         </is>
       </c>
       <c r="J34" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34" s="0" t="inlineStr">
         <is>
-          <t>可用参数: {actor} {skill}</t>
+          <t>可用参数: {actor} {target}</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="H35" s="0" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Skill</t>
         </is>
       </c>
       <c r="I35" s="0" t="inlineStr">
         <is>
-          <t>造成伤害</t>
+          <t>释放技能</t>
         </is>
       </c>
       <c r="J35" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K35" s="0" t="inlineStr">
         <is>
-          <t>可用参数: {actor} {target} {value}</t>
+          <t>可用参数: {actor} {skill}</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="H36" s="0" t="inlineStr">
         <is>
-          <t>Heal</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="I36" s="0" t="inlineStr">
         <is>
-          <t>治疗回血</t>
+          <t>造成伤害</t>
         </is>
       </c>
       <c r="J36" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K36" s="0" t="inlineStr">
         <is>
-          <t>可用参数: {actor} {value}</t>
+          <t>可用参数: {actor} {target} {value}</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="H37" s="0" t="inlineStr">
         <is>
-          <t>Buff</t>
+          <t>Heal</t>
         </is>
       </c>
       <c r="I37" s="0" t="inlineStr">
         <is>
-          <t>获得Buff</t>
+          <t>治疗回血</t>
         </is>
       </c>
       <c r="J37" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K37" s="0" t="inlineStr">
         <is>
-          <t>可用参数: {actor} {extra}</t>
+          <t>可用参数: {actor} {value}</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="H38" s="0" t="inlineStr">
         <is>
-          <t>Dodge</t>
+          <t>Buff</t>
         </is>
       </c>
       <c r="I38" s="0" t="inlineStr">
         <is>
-          <t>打空</t>
+          <t>获得Buff</t>
         </is>
       </c>
       <c r="J38" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K38" s="0" t="inlineStr">
         <is>
-          <t>可用参数: {actor} {skill}</t>
+          <t>可用参数: {actor} {extra}</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="H39" s="0" t="inlineStr">
         <is>
-          <t>Death</t>
+          <t>Dodge</t>
         </is>
       </c>
       <c r="I39" s="0" t="inlineStr">
         <is>
-          <t>死亡</t>
+          <t>打空</t>
         </is>
       </c>
       <c r="J39" s="0" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K39" s="0" t="inlineStr">
         <is>
-          <t>可用参数: {actor} {extra}</t>
+          <t>可用参数: {actor} {skill}</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="H40" s="0" t="inlineStr">
         <is>
-          <t>End</t>
+          <t>Death</t>
         </is>
       </c>
       <c r="I40" s="0" t="inlineStr">
         <is>
-          <t>战斗结束</t>
+          <t>死亡</t>
         </is>
       </c>
       <c r="J40" s="0" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K40" s="0" t="inlineStr">
         <is>
@@ -1933,80 +1933,343 @@
     <row r="41">
       <c r="H41" s="0" t="inlineStr">
         <is>
-          <t>BuffApply</t>
+          <t>End</t>
         </is>
       </c>
       <c r="I41" s="0" t="inlineStr">
         <is>
-          <t>施加Buff</t>
+          <t>战斗结束</t>
         </is>
       </c>
       <c r="J41" s="0" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K41" s="0" t="inlineStr">
         <is>
-          <t>可用参数: {actor} {target} {extra}</t>
+          <t>可用参数: {actor} {extra}</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="H42" s="0" t="inlineStr">
         <is>
-          <t>BuffRemove</t>
+          <t>BuffApply</t>
         </is>
       </c>
       <c r="I42" s="0" t="inlineStr">
         <is>
-          <t>Buff消失</t>
+          <t>施加Buff</t>
         </is>
       </c>
       <c r="J42" s="0" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K42" s="0" t="inlineStr">
         <is>
-          <t>可用参数: {target} {extra}</t>
+          <t>可用参数: {actor} {target} {extra}</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="H43" s="0" t="inlineStr">
         <is>
-          <t>BuffTick</t>
+          <t>BuffRemove</t>
         </is>
       </c>
       <c r="I43" s="0" t="inlineStr">
         <is>
-          <t>Buff持续伤害</t>
+          <t>Buff消失</t>
         </is>
       </c>
       <c r="J43" s="0" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K43" s="0" t="inlineStr">
         <is>
-          <t>可用参数: {target} {extra} {value}</t>
+          <t>可用参数: {target} {extra}</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="H44" s="0" t="inlineStr">
         <is>
+          <t>BuffTick</t>
+        </is>
+      </c>
+      <c r="I44" s="0" t="inlineStr">
+        <is>
+          <t>Buff持续伤害</t>
+        </is>
+      </c>
+      <c r="J44" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="K44" s="0" t="inlineStr">
+        <is>
+          <t>可用参数: {target} {extra} {value}</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="H45" s="0" t="inlineStr">
+        <is>
           <t>ShieldAbsorb</t>
         </is>
       </c>
-      <c r="I44" s="0" t="inlineStr">
+      <c r="I45" s="0" t="inlineStr">
         <is>
           <t>护盾吸收</t>
         </is>
       </c>
-      <c r="J44" s="0" t="n">
+      <c r="J45" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="K44" s="0" t="inlineStr">
+      <c r="K45" s="0" t="inlineStr">
         <is>
           <t>可用参数: {target} {value}</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="0" t="inlineStr">
+        <is>
+          <t>common.ERespawnType</t>
+        </is>
+      </c>
+      <c r="B46" s="0" t="inlineStr">
+        <is>
+          <t>common.ERespawnType</t>
+        </is>
+      </c>
+      <c r="C46" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="D46" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="F46" s="0" t="inlineStr">
+        <is>
+          <t>怪物复活类型</t>
+        </is>
+      </c>
+      <c r="H46" s="0" t="inlineStr">
+        <is>
+          <t>SpawnPoint</t>
+        </is>
+      </c>
+      <c r="I46" s="0" t="inlineStr">
+        <is>
+          <t>出生点</t>
+        </is>
+      </c>
+      <c r="J46" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="0" t="inlineStr">
+        <is>
+          <t>在出生点复活</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="H47" s="0" t="inlineStr">
+        <is>
+          <t>DeathPoint</t>
+        </is>
+      </c>
+      <c r="I47" s="0" t="inlineStr">
+        <is>
+          <t>死亡点</t>
+        </is>
+      </c>
+      <c r="J47" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" s="0" t="inlineStr">
+        <is>
+          <t>在死亡位置复活</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="H48" s="0" t="inlineStr">
+        <is>
+          <t>RandomNearSpawn</t>
+        </is>
+      </c>
+      <c r="I48" s="0" t="inlineStr">
+        <is>
+          <t>出生点附近随机</t>
+        </is>
+      </c>
+      <c r="J48" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K48" s="0" t="inlineStr">
+        <is>
+          <t>在出生点附近随机位置复活</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="0" t="inlineStr">
+        <is>
+          <t>common.EBuffType</t>
+        </is>
+      </c>
+      <c r="B49" s="0" t="inlineStr">
+        <is>
+          <t>common.EBuffType</t>
+        </is>
+      </c>
+      <c r="C49" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="D49" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="F49" s="0" t="inlineStr">
+        <is>
+          <t>Buff类型</t>
+        </is>
+      </c>
+      <c r="H49" s="0" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="I49" s="0" t="inlineStr">
+        <is>
+          <t>增益</t>
+        </is>
+      </c>
+      <c r="J49" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" s="0" t="inlineStr">
+        <is>
+          <t>增益效果</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="H50" s="0" t="inlineStr">
+        <is>
+          <t>Debuff</t>
+        </is>
+      </c>
+      <c r="I50" s="0" t="inlineStr">
+        <is>
+          <t>减益</t>
+        </is>
+      </c>
+      <c r="J50" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K50" s="0" t="inlineStr">
+        <is>
+          <t>减益效果</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>common.ECombatBehaviorType</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>common.ECombatBehaviorType</t>
+        </is>
+      </c>
+      <c r="C51" t="b">
+        <v>0</v>
+      </c>
+      <c r="D51" t="b">
+        <v>1</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>战斗行为类型</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>自动</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>根据技能自动推断</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Melee</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>近战</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>1</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>近战追击</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Ranged</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>远程</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>2</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>远程攻击</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Caster</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>法师</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>3</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>施法者</t>
         </is>
       </c>
     </row>

--- a/tables/datas/__enums__.xlsx
+++ b/tables/datas/__enums__.xlsx
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L54"/>
+  <dimension ref="A1:L79"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" style="2" min="2" max="2"/>
@@ -2173,104 +2173,481 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="0" t="inlineStr">
         <is>
           <t>common.ECombatBehaviorType</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="0" t="inlineStr">
         <is>
           <t>common.ECombatBehaviorType</t>
         </is>
       </c>
-      <c r="C51" t="b">
+      <c r="C51" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D51" t="b">
+      <c r="D51" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F51" s="0" t="inlineStr">
         <is>
           <t>战斗行为类型</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H51" s="0" t="inlineStr">
         <is>
           <t>Auto</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="I51" s="0" t="inlineStr">
         <is>
           <t>自动</t>
         </is>
       </c>
-      <c r="J51" t="n">
+      <c r="J51" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="K51" s="0" t="inlineStr">
         <is>
           <t>根据技能自动推断</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="H52" t="inlineStr">
+      <c r="H52" s="0" t="inlineStr">
         <is>
           <t>Melee</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="I52" s="0" t="inlineStr">
         <is>
           <t>近战</t>
         </is>
       </c>
-      <c r="J52" t="n">
+      <c r="J52" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="K52" s="0" t="inlineStr">
         <is>
           <t>近战追击</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="H53" t="inlineStr">
+      <c r="H53" s="0" t="inlineStr">
         <is>
           <t>Ranged</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="I53" s="0" t="inlineStr">
         <is>
           <t>远程</t>
         </is>
       </c>
-      <c r="J53" t="n">
+      <c r="J53" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="K53" s="0" t="inlineStr">
         <is>
           <t>远程攻击</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="H54" t="inlineStr">
+      <c r="H54" s="0" t="inlineStr">
         <is>
           <t>Caster</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="I54" s="0" t="inlineStr">
         <is>
           <t>法师</t>
         </is>
       </c>
-      <c r="J54" t="n">
+      <c r="J54" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="K54" s="0" t="inlineStr">
         <is>
           <t>施法者</t>
         </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>common.ESkillId</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>技能ID枚举</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Slash</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>烈斩</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>ShieldBash</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>盾击</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Whirlwind</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>旋风斩</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>FireBall</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>火球术</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>FrostNova</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>冰霜新星</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>ArcaneMissile</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>奥术飞弹</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Heal</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>治疗术</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>HolyLight</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>神圣之光</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Smite</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>惩击</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Bite</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>撕咬</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Howl</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>狼嚎</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>SkeletorStrike</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>骷髅突刺</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>BattleShout</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>战吼</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>StoneSkin</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>石肤术</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>PoisonFog</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>毒雾</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Freeze</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>冰冻术</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>HolyShield</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>神圣护盾</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Blessing</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>祝福</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>VenomBite</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>猛毒撕咬</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>IceBreath</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>寒冰吐息</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Taunt</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>挑衅</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Ignite</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>燃烧</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Purify</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>净化</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Berserk</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>狂暴</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/tables/datas/__enums__.xlsx
+++ b/tables/datas/__enums__.xlsx
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L79"/>
+  <dimension ref="A1:L80"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" style="2" min="2" max="2"/>
@@ -1596,353 +1596,353 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="0" t="inlineStr">
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>SpawnProjectile</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>生成投射物</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>7</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>生成投射物</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="inlineStr">
         <is>
           <t>common.EDamageType</t>
         </is>
       </c>
-      <c r="B26" s="0" t="inlineStr">
+      <c r="B27" s="0" t="inlineStr">
         <is>
           <t>common.EDamageType</t>
         </is>
       </c>
-      <c r="C26" s="0" t="b">
+      <c r="C27" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D26" s="0" t="b">
+      <c r="D27" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="F26" s="0" t="inlineStr">
+      <c r="F27" s="0" t="inlineStr">
         <is>
           <t>伤害类型</t>
         </is>
       </c>
-      <c r="H26" s="0" t="inlineStr">
+      <c r="H27" s="0" t="inlineStr">
         <is>
           <t>Physical</t>
         </is>
       </c>
-      <c r="I26" s="0" t="inlineStr">
+      <c r="I27" s="0" t="inlineStr">
         <is>
           <t>物理</t>
         </is>
       </c>
-      <c r="J26" s="0" t="n">
+      <c r="J27" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="K26" s="0" t="inlineStr">
+      <c r="K27" s="0" t="inlineStr">
         <is>
           <t>物理</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="H27" s="0" t="inlineStr">
+    <row r="28">
+      <c r="H28" s="0" t="inlineStr">
         <is>
           <t>Magical</t>
         </is>
       </c>
-      <c r="I27" s="0" t="inlineStr">
+      <c r="I28" s="0" t="inlineStr">
         <is>
           <t>魔法</t>
         </is>
       </c>
-      <c r="J27" s="0" t="n">
+      <c r="J28" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="K27" s="0" t="inlineStr">
+      <c r="K28" s="0" t="inlineStr">
         <is>
           <t>魔法</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="0" t="inlineStr">
+    <row r="29">
+      <c r="B29" s="0" t="inlineStr">
         <is>
           <t>common.EJobType</t>
         </is>
       </c>
-      <c r="C28" s="0" t="b">
+      <c r="C29" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D28" s="0" t="b">
+      <c r="D29" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="G28" s="0" t="inlineStr">
+      <c r="G29" s="0" t="inlineStr">
         <is>
           <t>职业类型</t>
         </is>
       </c>
-      <c r="H28" s="0" t="inlineStr">
+      <c r="H29" s="0" t="inlineStr">
         <is>
           <t>Warrior</t>
         </is>
       </c>
-      <c r="I28" s="0" t="inlineStr">
+      <c r="I29" s="0" t="inlineStr">
         <is>
           <t>战士</t>
         </is>
       </c>
-      <c r="J28" s="0" t="n">
+      <c r="J29" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="K28" s="0" t="inlineStr">
+      <c r="K29" s="0" t="inlineStr">
         <is>
           <t>战士</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="H29" s="0" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="I29" s="0" t="inlineStr">
-        <is>
-          <t>通用</t>
-        </is>
-      </c>
-      <c r="J29" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="0" t="inlineStr">
-        <is>
-          <t>通用</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="H30" s="0" t="inlineStr">
         <is>
-          <t>Mage</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="I30" s="0" t="inlineStr">
         <is>
-          <t>法师</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="J30" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K30" s="0" t="inlineStr">
         <is>
-          <t>法师</t>
+          <t>通用</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="H31" s="0" t="inlineStr">
         <is>
-          <t>Priest</t>
+          <t>Mage</t>
         </is>
       </c>
       <c r="I31" s="0" t="inlineStr">
         <is>
-          <t>牧师</t>
+          <t>法师</t>
         </is>
       </c>
       <c r="J31" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K31" s="0" t="inlineStr">
         <is>
-          <t>牧师</t>
+          <t>法师</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="H32" s="0" t="inlineStr">
         <is>
+          <t>Priest</t>
+        </is>
+      </c>
+      <c r="I32" s="0" t="inlineStr">
+        <is>
+          <t>牧师</t>
+        </is>
+      </c>
+      <c r="J32" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="K32" s="0" t="inlineStr">
+        <is>
+          <t>牧师</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="H33" s="0" t="inlineStr">
+        <is>
           <t>Monster</t>
         </is>
       </c>
-      <c r="I32" s="0" t="inlineStr">
+      <c r="I33" s="0" t="inlineStr">
         <is>
           <t>怪物</t>
         </is>
       </c>
-      <c r="J32" s="0" t="n">
+      <c r="J33" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="K32" s="0" t="inlineStr">
+      <c r="K33" s="0" t="inlineStr">
         <is>
           <t>怪物</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="0" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="0" t="inlineStr">
         <is>
           <t>common.ECombatLogType</t>
         </is>
       </c>
-      <c r="B33" s="0" t="b">
+      <c r="B34" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="C33" s="0" t="b">
+      <c r="C34" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="G33" s="0" t="inlineStr">
+      <c r="G34" s="0" t="inlineStr">
         <is>
           <t>战斗日志文本类型</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="H34" s="0" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="I34" s="0" t="inlineStr">
-        <is>
-          <t>战斗开始</t>
-        </is>
-      </c>
-      <c r="J34" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" s="0" t="inlineStr">
-        <is>
-          <t>可用参数: {actor} {target}</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="H35" s="0" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="I35" s="0" t="inlineStr">
         <is>
-          <t>释放技能</t>
+          <t>战斗开始</t>
         </is>
       </c>
       <c r="J35" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" s="0" t="inlineStr">
         <is>
-          <t>可用参数: {actor} {skill}</t>
+          <t>可用参数: {actor} {target}</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="H36" s="0" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Skill</t>
         </is>
       </c>
       <c r="I36" s="0" t="inlineStr">
         <is>
-          <t>造成伤害</t>
+          <t>释放技能</t>
         </is>
       </c>
       <c r="J36" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K36" s="0" t="inlineStr">
         <is>
-          <t>可用参数: {actor} {target} {value}</t>
+          <t>可用参数: {actor} {skill}</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="H37" s="0" t="inlineStr">
         <is>
-          <t>Heal</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="I37" s="0" t="inlineStr">
         <is>
-          <t>治疗回血</t>
+          <t>造成伤害</t>
         </is>
       </c>
       <c r="J37" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K37" s="0" t="inlineStr">
         <is>
-          <t>可用参数: {actor} {value}</t>
+          <t>可用参数: {actor} {target} {value}</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="H38" s="0" t="inlineStr">
         <is>
-          <t>Buff</t>
+          <t>Heal</t>
         </is>
       </c>
       <c r="I38" s="0" t="inlineStr">
         <is>
-          <t>获得Buff</t>
+          <t>治疗回血</t>
         </is>
       </c>
       <c r="J38" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K38" s="0" t="inlineStr">
         <is>
-          <t>可用参数: {actor} {extra}</t>
+          <t>可用参数: {actor} {value}</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="H39" s="0" t="inlineStr">
         <is>
-          <t>Dodge</t>
+          <t>Buff</t>
         </is>
       </c>
       <c r="I39" s="0" t="inlineStr">
         <is>
-          <t>打空</t>
+          <t>获得Buff</t>
         </is>
       </c>
       <c r="J39" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K39" s="0" t="inlineStr">
         <is>
-          <t>可用参数: {actor} {skill}</t>
+          <t>可用参数: {actor} {extra}</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="H40" s="0" t="inlineStr">
         <is>
-          <t>Death</t>
+          <t>Dodge</t>
         </is>
       </c>
       <c r="I40" s="0" t="inlineStr">
         <is>
-          <t>死亡</t>
+          <t>打空</t>
         </is>
       </c>
       <c r="J40" s="0" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K40" s="0" t="inlineStr">
         <is>
-          <t>可用参数: {actor} {extra}</t>
+          <t>可用参数: {actor} {skill}</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="H41" s="0" t="inlineStr">
         <is>
-          <t>End</t>
+          <t>Death</t>
         </is>
       </c>
       <c r="I41" s="0" t="inlineStr">
         <is>
-          <t>战斗结束</t>
+          <t>死亡</t>
         </is>
       </c>
       <c r="J41" s="0" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K41" s="0" t="inlineStr">
         <is>
@@ -1953,700 +1953,720 @@
     <row r="42">
       <c r="H42" s="0" t="inlineStr">
         <is>
-          <t>BuffApply</t>
+          <t>End</t>
         </is>
       </c>
       <c r="I42" s="0" t="inlineStr">
         <is>
-          <t>施加Buff</t>
+          <t>战斗结束</t>
         </is>
       </c>
       <c r="J42" s="0" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K42" s="0" t="inlineStr">
         <is>
-          <t>可用参数: {actor} {target} {extra}</t>
+          <t>可用参数: {actor} {extra}</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="H43" s="0" t="inlineStr">
         <is>
-          <t>BuffRemove</t>
+          <t>BuffApply</t>
         </is>
       </c>
       <c r="I43" s="0" t="inlineStr">
         <is>
-          <t>Buff消失</t>
+          <t>施加Buff</t>
         </is>
       </c>
       <c r="J43" s="0" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K43" s="0" t="inlineStr">
         <is>
-          <t>可用参数: {target} {extra}</t>
+          <t>可用参数: {actor} {target} {extra}</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="H44" s="0" t="inlineStr">
         <is>
-          <t>BuffTick</t>
+          <t>BuffRemove</t>
         </is>
       </c>
       <c r="I44" s="0" t="inlineStr">
         <is>
-          <t>Buff持续伤害</t>
+          <t>Buff消失</t>
         </is>
       </c>
       <c r="J44" s="0" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K44" s="0" t="inlineStr">
         <is>
-          <t>可用参数: {target} {extra} {value}</t>
+          <t>可用参数: {target} {extra}</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="H45" s="0" t="inlineStr">
         <is>
+          <t>BuffTick</t>
+        </is>
+      </c>
+      <c r="I45" s="0" t="inlineStr">
+        <is>
+          <t>Buff持续伤害</t>
+        </is>
+      </c>
+      <c r="J45" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="K45" s="0" t="inlineStr">
+        <is>
+          <t>可用参数: {target} {extra} {value}</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="H46" s="0" t="inlineStr">
+        <is>
           <t>ShieldAbsorb</t>
         </is>
       </c>
-      <c r="I45" s="0" t="inlineStr">
+      <c r="I46" s="0" t="inlineStr">
         <is>
           <t>护盾吸收</t>
         </is>
       </c>
-      <c r="J45" s="0" t="n">
+      <c r="J46" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="K45" s="0" t="inlineStr">
+      <c r="K46" s="0" t="inlineStr">
         <is>
           <t>可用参数: {target} {value}</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="0" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="0" t="inlineStr">
         <is>
           <t>common.ERespawnType</t>
         </is>
       </c>
-      <c r="B46" s="0" t="inlineStr">
+      <c r="B47" s="0" t="inlineStr">
         <is>
           <t>common.ERespawnType</t>
         </is>
       </c>
-      <c r="C46" s="0" t="b">
+      <c r="C47" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D46" s="0" t="b">
+      <c r="D47" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="F46" s="0" t="inlineStr">
+      <c r="F47" s="0" t="inlineStr">
         <is>
           <t>怪物复活类型</t>
         </is>
       </c>
-      <c r="H46" s="0" t="inlineStr">
+      <c r="H47" s="0" t="inlineStr">
         <is>
           <t>SpawnPoint</t>
         </is>
       </c>
-      <c r="I46" s="0" t="inlineStr">
+      <c r="I47" s="0" t="inlineStr">
         <is>
           <t>出生点</t>
         </is>
       </c>
-      <c r="J46" s="0" t="n">
+      <c r="J47" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="K46" s="0" t="inlineStr">
+      <c r="K47" s="0" t="inlineStr">
         <is>
           <t>在出生点复活</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="H47" s="0" t="inlineStr">
-        <is>
-          <t>DeathPoint</t>
-        </is>
-      </c>
-      <c r="I47" s="0" t="inlineStr">
-        <is>
-          <t>死亡点</t>
-        </is>
-      </c>
-      <c r="J47" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K47" s="0" t="inlineStr">
-        <is>
-          <t>在死亡位置复活</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="H48" s="0" t="inlineStr">
         <is>
+          <t>DeathPoint</t>
+        </is>
+      </c>
+      <c r="I48" s="0" t="inlineStr">
+        <is>
+          <t>死亡点</t>
+        </is>
+      </c>
+      <c r="J48" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" s="0" t="inlineStr">
+        <is>
+          <t>在死亡位置复活</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="H49" s="0" t="inlineStr">
+        <is>
           <t>RandomNearSpawn</t>
         </is>
       </c>
-      <c r="I48" s="0" t="inlineStr">
+      <c r="I49" s="0" t="inlineStr">
         <is>
           <t>出生点附近随机</t>
         </is>
       </c>
-      <c r="J48" s="0" t="n">
+      <c r="J49" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="K48" s="0" t="inlineStr">
+      <c r="K49" s="0" t="inlineStr">
         <is>
           <t>在出生点附近随机位置复活</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="0" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="0" t="inlineStr">
         <is>
           <t>common.EBuffType</t>
         </is>
       </c>
-      <c r="B49" s="0" t="inlineStr">
+      <c r="B50" s="0" t="inlineStr">
         <is>
           <t>common.EBuffType</t>
         </is>
       </c>
-      <c r="C49" s="0" t="b">
+      <c r="C50" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D49" s="0" t="b">
+      <c r="D50" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="F49" s="0" t="inlineStr">
+      <c r="F50" s="0" t="inlineStr">
         <is>
           <t>Buff类型</t>
         </is>
       </c>
-      <c r="H49" s="0" t="inlineStr">
+      <c r="H50" s="0" t="inlineStr">
         <is>
           <t>Buff</t>
         </is>
       </c>
-      <c r="I49" s="0" t="inlineStr">
+      <c r="I50" s="0" t="inlineStr">
         <is>
           <t>增益</t>
         </is>
       </c>
-      <c r="J49" s="0" t="n">
+      <c r="J50" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="K49" s="0" t="inlineStr">
+      <c r="K50" s="0" t="inlineStr">
         <is>
           <t>增益效果</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="H50" s="0" t="inlineStr">
+    <row r="51">
+      <c r="H51" s="0" t="inlineStr">
         <is>
           <t>Debuff</t>
         </is>
       </c>
-      <c r="I50" s="0" t="inlineStr">
+      <c r="I51" s="0" t="inlineStr">
         <is>
           <t>减益</t>
         </is>
       </c>
-      <c r="J50" s="0" t="n">
+      <c r="J51" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="K50" s="0" t="inlineStr">
+      <c r="K51" s="0" t="inlineStr">
         <is>
           <t>减益效果</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="0" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="0" t="inlineStr">
         <is>
           <t>common.ECombatBehaviorType</t>
         </is>
       </c>
-      <c r="B51" s="0" t="inlineStr">
+      <c r="B52" s="0" t="inlineStr">
         <is>
           <t>common.ECombatBehaviorType</t>
         </is>
       </c>
-      <c r="C51" s="0" t="b">
+      <c r="C52" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D51" s="0" t="b">
+      <c r="D52" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="F51" s="0" t="inlineStr">
+      <c r="F52" s="0" t="inlineStr">
         <is>
           <t>战斗行为类型</t>
         </is>
       </c>
-      <c r="H51" s="0" t="inlineStr">
+      <c r="H52" s="0" t="inlineStr">
         <is>
           <t>Auto</t>
         </is>
       </c>
-      <c r="I51" s="0" t="inlineStr">
+      <c r="I52" s="0" t="inlineStr">
         <is>
           <t>自动</t>
         </is>
       </c>
-      <c r="J51" s="0" t="n">
+      <c r="J52" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="K51" s="0" t="inlineStr">
+      <c r="K52" s="0" t="inlineStr">
         <is>
           <t>根据技能自动推断</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="H52" s="0" t="inlineStr">
-        <is>
-          <t>Melee</t>
-        </is>
-      </c>
-      <c r="I52" s="0" t="inlineStr">
-        <is>
-          <t>近战</t>
-        </is>
-      </c>
-      <c r="J52" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K52" s="0" t="inlineStr">
-        <is>
-          <t>近战追击</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="H53" s="0" t="inlineStr">
         <is>
-          <t>Ranged</t>
+          <t>Melee</t>
         </is>
       </c>
       <c r="I53" s="0" t="inlineStr">
         <is>
-          <t>远程</t>
+          <t>近战</t>
         </is>
       </c>
       <c r="J53" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K53" s="0" t="inlineStr">
         <is>
-          <t>远程攻击</t>
+          <t>近战追击</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="H54" s="0" t="inlineStr">
         <is>
+          <t>Ranged</t>
+        </is>
+      </c>
+      <c r="I54" s="0" t="inlineStr">
+        <is>
+          <t>远程</t>
+        </is>
+      </c>
+      <c r="J54" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K54" s="0" t="inlineStr">
+        <is>
+          <t>远程攻击</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="H55" s="0" t="inlineStr">
+        <is>
           <t>Caster</t>
         </is>
       </c>
-      <c r="I54" s="0" t="inlineStr">
+      <c r="I55" s="0" t="inlineStr">
         <is>
           <t>法师</t>
         </is>
       </c>
-      <c r="J54" s="0" t="n">
+      <c r="J55" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="K54" s="0" t="inlineStr">
+      <c r="K55" s="0" t="inlineStr">
         <is>
           <t>施法者</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="B55" t="inlineStr">
+    <row r="56">
+      <c r="B56" s="0" t="inlineStr">
         <is>
           <t>common.ESkillId</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D56" s="0" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F56" s="0" t="inlineStr">
         <is>
           <t>技能ID枚举</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="H56" t="inlineStr">
+    <row r="57">
+      <c r="H57" s="0" t="inlineStr">
         <is>
           <t>Slash</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="I57" s="0" t="inlineStr">
         <is>
           <t>烈斩</t>
         </is>
       </c>
-      <c r="J56" t="n">
+      <c r="J57" s="0" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="57">
-      <c r="H57" t="inlineStr">
+    <row r="58">
+      <c r="H58" s="0" t="inlineStr">
         <is>
           <t>ShieldBash</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="I58" s="0" t="inlineStr">
         <is>
           <t>盾击</t>
         </is>
       </c>
-      <c r="J57" t="n">
+      <c r="J58" s="0" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="58">
-      <c r="H58" t="inlineStr">
+    <row r="59">
+      <c r="H59" s="0" t="inlineStr">
         <is>
           <t>Whirlwind</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="I59" s="0" t="inlineStr">
         <is>
           <t>旋风斩</t>
         </is>
       </c>
-      <c r="J58" t="n">
+      <c r="J59" s="0" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="59">
-      <c r="H59" t="inlineStr">
+    <row r="60">
+      <c r="H60" s="0" t="inlineStr">
         <is>
           <t>FireBall</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="I60" s="0" t="inlineStr">
         <is>
           <t>火球术</t>
         </is>
       </c>
-      <c r="J59" t="n">
+      <c r="J60" s="0" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="60">
-      <c r="H60" t="inlineStr">
+    <row r="61">
+      <c r="H61" s="0" t="inlineStr">
         <is>
           <t>FrostNova</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="I61" s="0" t="inlineStr">
         <is>
           <t>冰霜新星</t>
         </is>
       </c>
-      <c r="J60" t="n">
+      <c r="J61" s="0" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="61">
-      <c r="H61" t="inlineStr">
+    <row r="62">
+      <c r="H62" s="0" t="inlineStr">
         <is>
           <t>ArcaneMissile</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="I62" s="0" t="inlineStr">
         <is>
           <t>奥术飞弹</t>
         </is>
       </c>
-      <c r="J61" t="n">
+      <c r="J62" s="0" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="62">
-      <c r="H62" t="inlineStr">
+    <row r="63">
+      <c r="H63" s="0" t="inlineStr">
         <is>
           <t>Heal</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="I63" s="0" t="inlineStr">
         <is>
           <t>治疗术</t>
         </is>
       </c>
-      <c r="J62" t="n">
+      <c r="J63" s="0" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="63">
-      <c r="H63" t="inlineStr">
+    <row r="64">
+      <c r="H64" s="0" t="inlineStr">
         <is>
           <t>HolyLight</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="I64" s="0" t="inlineStr">
         <is>
           <t>神圣之光</t>
         </is>
       </c>
-      <c r="J63" t="n">
+      <c r="J64" s="0" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="64">
-      <c r="H64" t="inlineStr">
+    <row r="65">
+      <c r="H65" s="0" t="inlineStr">
         <is>
           <t>Smite</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="I65" s="0" t="inlineStr">
         <is>
           <t>惩击</t>
         </is>
       </c>
-      <c r="J64" t="n">
+      <c r="J65" s="0" t="n">
         <v>11</v>
       </c>
     </row>
-    <row r="65">
-      <c r="H65" t="inlineStr">
+    <row r="66">
+      <c r="H66" s="0" t="inlineStr">
         <is>
           <t>Bite</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="I66" s="0" t="inlineStr">
         <is>
           <t>撕咬</t>
         </is>
       </c>
-      <c r="J65" t="n">
+      <c r="J66" s="0" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="66">
-      <c r="H66" t="inlineStr">
+    <row r="67">
+      <c r="H67" s="0" t="inlineStr">
         <is>
           <t>Howl</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="I67" s="0" t="inlineStr">
         <is>
           <t>狼嚎</t>
         </is>
       </c>
-      <c r="J66" t="n">
+      <c r="J67" s="0" t="n">
         <v>13</v>
       </c>
     </row>
-    <row r="67">
-      <c r="H67" t="inlineStr">
+    <row r="68">
+      <c r="H68" s="0" t="inlineStr">
         <is>
           <t>SkeletorStrike</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="I68" s="0" t="inlineStr">
         <is>
           <t>骷髅突刺</t>
         </is>
       </c>
-      <c r="J67" t="n">
+      <c r="J68" s="0" t="n">
         <v>14</v>
       </c>
     </row>
-    <row r="68">
-      <c r="H68" t="inlineStr">
+    <row r="69">
+      <c r="H69" s="0" t="inlineStr">
         <is>
           <t>BattleShout</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="I69" s="0" t="inlineStr">
         <is>
           <t>战吼</t>
         </is>
       </c>
-      <c r="J68" t="n">
+      <c r="J69" s="0" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="69">
-      <c r="H69" t="inlineStr">
+    <row r="70">
+      <c r="H70" s="0" t="inlineStr">
         <is>
           <t>StoneSkin</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="I70" s="0" t="inlineStr">
         <is>
           <t>石肤术</t>
         </is>
       </c>
-      <c r="J69" t="n">
+      <c r="J70" s="0" t="n">
         <v>21</v>
       </c>
     </row>
-    <row r="70">
-      <c r="H70" t="inlineStr">
+    <row r="71">
+      <c r="H71" s="0" t="inlineStr">
         <is>
           <t>PoisonFog</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="I71" s="0" t="inlineStr">
         <is>
           <t>毒雾</t>
         </is>
       </c>
-      <c r="J70" t="n">
+      <c r="J71" s="0" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="71">
-      <c r="H71" t="inlineStr">
+    <row r="72">
+      <c r="H72" s="0" t="inlineStr">
         <is>
           <t>Freeze</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="I72" s="0" t="inlineStr">
         <is>
           <t>冰冻术</t>
         </is>
       </c>
-      <c r="J71" t="n">
+      <c r="J72" s="0" t="n">
         <v>23</v>
       </c>
     </row>
-    <row r="72">
-      <c r="H72" t="inlineStr">
+    <row r="73">
+      <c r="H73" s="0" t="inlineStr">
         <is>
           <t>HolyShield</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="I73" s="0" t="inlineStr">
         <is>
           <t>神圣护盾</t>
         </is>
       </c>
-      <c r="J72" t="n">
+      <c r="J73" s="0" t="n">
         <v>24</v>
       </c>
     </row>
-    <row r="73">
-      <c r="H73" t="inlineStr">
+    <row r="74">
+      <c r="H74" s="0" t="inlineStr">
         <is>
           <t>Blessing</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="I74" s="0" t="inlineStr">
         <is>
           <t>祝福</t>
         </is>
       </c>
-      <c r="J73" t="n">
+      <c r="J74" s="0" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="74">
-      <c r="H74" t="inlineStr">
+    <row r="75">
+      <c r="H75" s="0" t="inlineStr">
         <is>
           <t>VenomBite</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="I75" s="0" t="inlineStr">
         <is>
           <t>猛毒撕咬</t>
         </is>
       </c>
-      <c r="J74" t="n">
+      <c r="J75" s="0" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="75">
-      <c r="H75" t="inlineStr">
+    <row r="76">
+      <c r="H76" s="0" t="inlineStr">
         <is>
           <t>IceBreath</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="I76" s="0" t="inlineStr">
         <is>
           <t>寒冰吐息</t>
         </is>
       </c>
-      <c r="J75" t="n">
+      <c r="J76" s="0" t="n">
         <v>27</v>
       </c>
     </row>
-    <row r="76">
-      <c r="H76" t="inlineStr">
+    <row r="77">
+      <c r="H77" s="0" t="inlineStr">
         <is>
           <t>Taunt</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="I77" s="0" t="inlineStr">
         <is>
           <t>挑衅</t>
         </is>
       </c>
-      <c r="J76" t="n">
+      <c r="J77" s="0" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="77">
-      <c r="H77" t="inlineStr">
+    <row r="78">
+      <c r="H78" s="0" t="inlineStr">
         <is>
           <t>Ignite</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="I78" s="0" t="inlineStr">
         <is>
           <t>燃烧</t>
         </is>
       </c>
-      <c r="J77" t="n">
+      <c r="J78" s="0" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="78">
-      <c r="H78" t="inlineStr">
+    <row r="79">
+      <c r="H79" s="0" t="inlineStr">
         <is>
           <t>Purify</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="I79" s="0" t="inlineStr">
         <is>
           <t>净化</t>
         </is>
       </c>
-      <c r="J78" t="n">
+      <c r="J79" s="0" t="n">
         <v>32</v>
       </c>
     </row>
-    <row r="79">
-      <c r="H79" t="inlineStr">
+    <row r="80">
+      <c r="H80" s="0" t="inlineStr">
         <is>
           <t>Berserk</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="I80" s="0" t="inlineStr">
         <is>
           <t>狂暴</t>
         </is>
       </c>
-      <c r="J79" t="n">
+      <c r="J80" s="0" t="n">
         <v>33</v>
       </c>
     </row>

--- a/tables/datas/__enums__.xlsx
+++ b/tables/datas/__enums__.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="15615" windowHeight="7560" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L80"/>
+  <dimension ref="A1:L83"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" style="2" min="2" max="2"/>
@@ -1596,20 +1596,20 @@
       </c>
     </row>
     <row r="26">
-      <c r="H26" t="inlineStr">
+      <c r="H26" s="0" t="inlineStr">
         <is>
           <t>SpawnProjectile</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I26" s="0" t="inlineStr">
         <is>
           <t>生成投射物</t>
         </is>
       </c>
-      <c r="J26" t="n">
+      <c r="J26" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K26" s="0" t="inlineStr">
         <is>
           <t>生成投射物</t>
         </is>
@@ -2668,6 +2668,81 @@
       </c>
       <c r="J80" s="0" t="n">
         <v>33</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>common.ENpcType</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>NPC类型</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>JobMaster</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>转职大师</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>1</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>转职大师</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Combatant</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>战斗NPC</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>2</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>可对话触发战斗</t>
+        </is>
       </c>
     </row>
   </sheetData>
